--- a/Resources/Data/GemData.xlsx
+++ b/Resources/Data/GemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\it242225\Documents\Visual Studio 2022\projects\二年生\オリジナル_テスト\CaveDiving\Resources\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEF9A06E-6DA4-4CED-A628-1B0BFA2A671A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AD610F2-68F3-44DE-AD25-38136C1478F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2220" yWindow="1392" windowWidth="19212" windowHeight="10692" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2568" yWindow="1548" windowWidth="19212" windowHeight="10692" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,19 +29,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
-  <si>
-    <t>効果</t>
-    <rPh sb="0" eb="2">
-      <t>コウカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="26">
   <si>
     <t>効果説明</t>
     <rPh sb="0" eb="2">
@@ -112,21 +108,70 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>emeraldpanel.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>rubypanel.png</t>
-  </si>
-  <si>
-    <t>rubypanel.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>sapphirepanel.png</t>
-  </si>
-  <si>
-    <t>frame.png</t>
+    <t>効果量</t>
+    <rPh sb="0" eb="2">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>リョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>効果間隔</t>
+    <rPh sb="0" eb="4">
+      <t>コウカカンカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クラス名（拡張子なし）</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>カクチョウシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アメジスト</t>
+  </si>
+  <si>
+    <t>StatusUpGem</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Gem/emeraldpanel.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Gem/rubypanel.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Gem/sapphirepanel.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Gem/frame.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HPAutoRecoveryGem</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トパーズ</t>
+  </si>
+  <si>
+    <t>攻撃をすべて回転攻撃にする</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>カイテンコウゲキ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -158,7 +203,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -192,14 +237,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -480,148 +539,173 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="13.19921875" customWidth="1"/>
     <col min="2" max="2" width="13.69921875" customWidth="1"/>
     <col min="3" max="3" width="17.5" customWidth="1"/>
     <col min="4" max="4" width="38" customWidth="1"/>
-    <col min="5" max="5" width="36.5" customWidth="1"/>
-    <col min="6" max="6" width="20.69921875" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
+    <col min="6" max="6" width="30.09765625" customWidth="1"/>
+    <col min="7" max="7" width="21.296875" customWidth="1"/>
+    <col min="8" max="8" width="20.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" s="1">
         <v>10</v>
       </c>
-      <c r="E2" s="1" t="str">
+      <c r="E2" s="1"/>
+      <c r="F2" s="1" t="str">
         <f>CONCATENATE(C2,"を",D2,"増加する")</f>
         <v>体力を10増加する</v>
       </c>
-      <c r="F2" t="s">
-        <v>15</v>
+      <c r="G2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" s="1">
         <v>10</v>
       </c>
-      <c r="E3" s="1" t="str">
-        <f t="shared" ref="E3:E8" si="0">CONCATENATE(C3,"を",D3,"増加する")</f>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1" t="str">
+        <f>CONCATENATE(C3,"を",D3,"増加する")</f>
         <v>攻撃力を10増加する</v>
       </c>
-      <c r="F3" t="s">
-        <v>17</v>
+      <c r="G3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" s="1">
         <v>10</v>
       </c>
-      <c r="E4" s="1" t="str">
-        <f t="shared" si="0"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1" t="str">
+        <f>CONCATENATE(C4,"を",D4,"増加する")</f>
         <v>防御力を10増加する</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="H4" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" s="1">
         <v>10</v>
       </c>
-      <c r="E5" s="1" t="str">
-        <f t="shared" si="0"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1" t="str">
+        <f>CONCATENATE(C5,"を",D5,"増加する")</f>
         <v>体力を10増加する</v>
       </c>
-      <c r="F5" t="s">
-        <v>15</v>
+      <c r="G5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="1">
-        <v>10</v>
-      </c>
-      <c r="E6" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>攻撃力を10増加する</v>
-      </c>
-      <c r="F6" t="s">
-        <v>16</v>
+        <v>5</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>5</v>
@@ -629,33 +713,43 @@
       <c r="D7" s="1">
         <v>10</v>
       </c>
-      <c r="E7" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>防御力を10増加する</v>
-      </c>
-      <c r="F7" t="s">
-        <v>18</v>
+      <c r="E7" s="1">
+        <v>5</v>
+      </c>
+      <c r="F7" s="1" t="str">
+        <f>CONCATENATE("HPを",E7,"秒ごとに",D7,"回復する")</f>
+        <v>HPを5秒ごとに10回復する</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8" s="1">
         <v>10</v>
       </c>
-      <c r="E8" s="1" t="str">
-        <f t="shared" si="0"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1" t="str">
+        <f>CONCATENATE(C8,"を",D8,"増加する")</f>
         <v>特殊を10増加する</v>
       </c>
-      <c r="F8" t="s">
-        <v>19</v>
+      <c r="G8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -664,8 +758,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C8" xr:uid="{3656DD66-B663-4BAF-9823-A65DEC9D1361}">
       <formula1>"体力,攻撃力,防御力,特殊"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B8" xr:uid="{99318863-A0A4-4C5C-A7B2-83B80F5A2DDE}">
-      <formula1>"エメラルド,ルビー,サファイア,ダイヤ"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B8" xr:uid="{4BE3F4FD-1CCD-4E1F-9242-C80D0E19C26C}">
+      <formula1>"エメラルド,ルビー,サファイア,ダイヤ,トパーズ,アクアマリン,モルガナイト,アメジスト"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Resources/Data/GemData.xlsx
+++ b/Resources/Data/GemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\it242225\Documents\Visual Studio 2022\projects\二年生\オリジナル_テスト\CaveDiving\Resources\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AD610F2-68F3-44DE-AD25-38136C1478F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3E416BA-A73C-49AC-8DED-956874DFEC5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2568" yWindow="1548" windowWidth="19212" windowHeight="10692" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="624" yWindow="1548" windowWidth="19212" windowHeight="10692" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
   <si>
     <t>効果説明</t>
     <rPh sb="0" eb="2">
@@ -172,6 +172,18 @@
     <rPh sb="6" eb="10">
       <t>カイテンコウゲキ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Gem/amethystpanel.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Gem/topazpanel.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AllSpenningAttackGem</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -694,10 +706,10 @@
         <v>25</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -724,7 +736,7 @@
         <v>23</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:8">

--- a/Resources/Data/GemData.xlsx
+++ b/Resources/Data/GemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\it242225\Documents\Visual Studio 2022\projects\二年生\オリジナル_テスト\CaveDiving\Resources\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3E416BA-A73C-49AC-8DED-956874DFEC5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB7949CE-BEBA-4EFB-9EF3-59BF8D03F6C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="624" yWindow="1548" windowWidth="19212" windowHeight="10692" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="19212" windowHeight="10692" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
   <si>
     <t>効果説明</t>
     <rPh sb="0" eb="2">
@@ -50,9 +50,6 @@
   </si>
   <si>
     <t>体力</t>
-  </si>
-  <si>
-    <t>体力</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -184,6 +181,17 @@
   </si>
   <si>
     <t>AllSpenningAttackGem</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アクアマリン</t>
+  </si>
+  <si>
+    <t>FullHPAttackUp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Gem/aquamarinepanel.png</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -559,35 +567,35 @@
     <col min="3" max="3" width="17.5" customWidth="1"/>
     <col min="4" max="4" width="38" customWidth="1"/>
     <col min="5" max="5" width="28" customWidth="1"/>
-    <col min="6" max="6" width="30.09765625" customWidth="1"/>
+    <col min="6" max="6" width="36.09765625" customWidth="1"/>
     <col min="7" max="7" width="21.296875" customWidth="1"/>
-    <col min="8" max="8" width="20.3984375" customWidth="1"/>
+    <col min="8" max="8" width="28.09765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -595,10 +603,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" s="1">
         <v>10</v>
@@ -609,10 +617,10 @@
         <v>体力を10増加する</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -620,10 +628,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" s="1">
         <v>10</v>
@@ -634,10 +642,10 @@
         <v>攻撃力を10増加する</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -645,10 +653,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" s="1">
         <v>10</v>
@@ -659,10 +667,10 @@
         <v>防御力を10増加する</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -670,24 +678,24 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="1">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="str">
-        <f>CONCATENATE(C5,"を",D5,"増加する")</f>
-        <v>体力を10増加する</v>
+        <f>CONCATENATE("HPが満タンのとき",C5,"を",D5,"増加する")</f>
+        <v>HPが満タンのとき攻撃力を25増加する</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -695,21 +703,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -717,26 +725,26 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="1">
         <v>5</v>
       </c>
-      <c r="D7" s="1">
+      <c r="E7" s="1">
         <v>10</v>
-      </c>
-      <c r="E7" s="1">
-        <v>5</v>
       </c>
       <c r="F7" s="1" t="str">
         <f>CONCATENATE("HPを",E7,"秒ごとに",D7,"回復する")</f>
-        <v>HPを5秒ごとに10回復する</v>
+        <v>HPを10秒ごとに5回復する</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -744,10 +752,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8" s="1">
         <v>10</v>
@@ -758,10 +766,10 @@
         <v>特殊を10増加する</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/Resources/Data/GemData.xlsx
+++ b/Resources/Data/GemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\it242225\Documents\Visual Studio 2022\projects\二年生\オリジナル_テスト\CaveDiving\Resources\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB7949CE-BEBA-4EFB-9EF3-59BF8D03F6C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1100DBE2-5C47-4927-A14F-52AEFB209403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1536" windowWidth="19212" windowHeight="10692" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="192" yWindow="1848" windowWidth="19212" windowHeight="10692" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="32">
   <si>
     <t>効果説明</t>
     <rPh sb="0" eb="2">
@@ -91,9 +91,6 @@
     <t>サファイア</t>
   </si>
   <si>
-    <t>ダイヤ</t>
-  </si>
-  <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -151,10 +148,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Gem/frame.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>HPAutoRecoveryGem</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -187,11 +180,22 @@
     <t>アクアマリン</t>
   </si>
   <si>
-    <t>FullHPAttackUp</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Gem/aquamarinepanel.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スピネル</t>
+  </si>
+  <si>
+    <t>GenerateShieldGem</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Gem/spinelpanel.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FullHPStatusUpGem</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -574,7 +578,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>6</v>
@@ -583,19 +587,19 @@
         <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -617,10 +621,10 @@
         <v>体力を10増加する</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -642,10 +646,10 @@
         <v>攻撃力を10増加する</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -667,10 +671,10 @@
         <v>防御力を10増加する</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -678,7 +682,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>2</v>
@@ -692,10 +696,10 @@
         <v>HPが満タンのとき攻撃力を25増加する</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -703,7 +707,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>4</v>
@@ -711,13 +715,13 @@
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -725,7 +729,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>4</v>
@@ -741,10 +745,10 @@
         <v>HPを10秒ごとに5回復する</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -752,34 +756,39 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1">
         <v>10</v>
       </c>
-      <c r="E8" s="1"/>
       <c r="F8" s="1" t="str">
-        <f>CONCATENATE(C8,"を",D8,"増加する")</f>
-        <v>特殊を10増加する</v>
+        <f>CONCATENATE(E8,"秒ごとにダメージを一度防ぐ盾を生成する")</f>
+        <v>10秒ごとにダメージを一度防ぐ盾を生成する</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C8" xr:uid="{3656DD66-B663-4BAF-9823-A65DEC9D1361}">
       <formula1>"体力,攻撃力,防御力,特殊"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B8" xr:uid="{4BE3F4FD-1CCD-4E1F-9242-C80D0E19C26C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B7" xr:uid="{4BE3F4FD-1CCD-4E1F-9242-C80D0E19C26C}">
       <formula1>"エメラルド,ルビー,サファイア,ダイヤ,トパーズ,アクアマリン,モルガナイト,アメジスト"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8" xr:uid="{3DCC796F-B3C6-4EDC-8FC1-3B4AD252486B}">
+      <formula1>"エメラルド,ルビー,サファイア,ダイヤ,トパーズ,アクアマリン,モルガナイト,アメジスト,スピネル"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
